--- a/Unit_Test_Plan_v0.1 InfySpringboard.xlsx
+++ b/Unit_Test_Plan_v0.1 InfySpringboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30516"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/kamaljeet_kaur01_ad_infosys_com1/Documents/Infosys/CC/Events/Oct 2021 - Mar 2022/CC2.0/Internship/Jan-Apr 2022/Artifacts/internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB76DAF0-B775-46EF-87C6-C0EC9E4586E4}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{76596F5D-7B59-4EAE-98D7-A4EC2BB24298}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="47">
   <si>
     <t>Sl: No:</t>
   </si>
@@ -56,7 +56,7 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>Planner Agent</t>
+    <t>Verifying agents</t>
   </si>
   <si>
     <t>Run test_planner_agent passing an empty state</t>
@@ -102,13 +102,88 @@
   </si>
   <si>
     <t>All agent nodes called, final status 'Completed'</t>
+  </si>
+  <si>
+    <t>Log Analyzer Tool Execution</t>
+  </si>
+  <si>
+    <t>Run test_log_analyzer fetching logs for a mocked service.</t>
+  </si>
+  <si>
+    <t>Verify the tool successfully parses mock_data.json and returns the log string.</t>
+  </si>
+  <si>
+    <t>Returns mocked log data string</t>
+  </si>
+  <si>
+    <t>Returned mocked log data string</t>
+  </si>
+  <si>
+    <t>Incident Action Invalid Input</t>
+  </si>
+  <si>
+    <t>Run test_incident_action_tool_invalid_action with action "delete".</t>
+  </si>
+  <si>
+    <t>Verify tool handles invalid actions without crashing.</t>
+  </si>
+  <si>
+    <t>Returns "Invalid action" error message</t>
+  </si>
+  <si>
+    <t>Returned "Invalid action" error message</t>
+  </si>
+  <si>
+    <t>External API HTTP Success</t>
+  </si>
+  <si>
+    <t>Run test_external_api_tool_success with mocked 200 OK response.</t>
+  </si>
+  <si>
+    <t>Verify the tool successfully parses standard HTTP responses.</t>
+  </si>
+  <si>
+    <t>Returns status code and latency string</t>
+  </si>
+  <si>
+    <t>Returned status code and latency string</t>
+  </si>
+  <si>
+    <t>External API Timeout</t>
+  </si>
+  <si>
+    <t>Run test_external_api_tool_timeout simulating a timeout exception.</t>
+  </si>
+  <si>
+    <t>Verify the tool safely catches requests.exceptions.Timeout.</t>
+  </si>
+  <si>
+    <t>Returns "timed out after 5 seconds" error</t>
+  </si>
+  <si>
+    <t>Caught timeout and returned error string</t>
+  </si>
+  <si>
+    <t>Investigation Agent ReAct Integration</t>
+  </si>
+  <si>
+    <t>Run agent with ReAct framework passing a mocked plan.</t>
+  </si>
+  <si>
+    <t>Verify the agent correctly identifies which tool to call based on the input text.</t>
+  </si>
+  <si>
+    <t>Tool is invoked and evidence string is returned</t>
+  </si>
+  <si>
+    <t>Tool invoked and evidence string returned</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -136,10 +211,21 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="-Apple-System"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color rgb="FF1F2328"/>
+      <color rgb="FF000000"/>
       <name val="Ui-Monospace"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -156,7 +242,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -166,23 +252,14 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
@@ -190,14 +267,14 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color indexed="64"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -205,20 +282,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -533,115 +619,215 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="55.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
-    <col min="5" max="5" width="23.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
+    <col min="3" max="3" width="62.5703125" customWidth="1"/>
+    <col min="4" max="4" width="68.7109375" customWidth="1"/>
+    <col min="5" max="5" width="45.7109375" customWidth="1"/>
     <col min="6" max="6" width="52.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="15.75">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="64.5">
-      <c r="A2" s="1">
+    <row r="2" spans="1:6" ht="15.75">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="48.75">
-      <c r="A3" s="1">
+    <row r="3" spans="1:6" ht="15.75">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="32.25">
-      <c r="A4" s="1">
+    <row r="4" spans="1:6" ht="15.75">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="48.75">
-      <c r="A5" s="1">
+    <row r="5" spans="1:6" ht="15.75">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="2" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="15">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="15">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="15">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="15">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
